--- a/AAII_Financials/Quarterly/MTEN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTEN_QTR_FIN.xlsx
@@ -1031,10 +1031,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
         <v>700</v>
@@ -1282,10 +1282,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1335,10 +1335,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3">
         <v>200</v>
@@ -1918,10 +1918,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -2442,10 +2442,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
         <v>0</v>
@@ -3014,10 +3014,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3600</v>
+        <v>3900</v>
       </c>
       <c r="E57" s="3">
-        <v>3600</v>
+        <v>3900</v>
       </c>
       <c r="F57" s="3">
         <v>1500</v>
@@ -3067,10 +3067,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="E58" s="3">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="F58" s="3">
         <v>1600</v>
@@ -3120,10 +3120,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3300</v>
+        <v>400</v>
       </c>
       <c r="E59" s="3">
-        <v>3300</v>
+        <v>400</v>
       </c>
       <c r="F59" s="3">
         <v>600</v>
